--- a/boq_styled.xlsx
+++ b/boq_styled.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -492,16 +492,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Finishes</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Floor Finish</t>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Floor Finishes</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Floor tiling to AD-02</t>
+          <t>Floor tiling</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -522,31 +522,31 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>89.56</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>15000</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>130500</v>
+        <v>1343400</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Wall Finish</t>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Wall Finishes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Plastering to walls in AD-02</t>
+          <t>Plastering to walls</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -555,31 +555,31 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>48.2</v>
+        <v>163.66</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>12000</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>578400</v>
+        <v>1963920</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Skirting</t>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Skirtings</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Skirting to AD-02</t>
+          <t>Skirting</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>13.39</v>
+        <v>49.36</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>2500</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>33475</v>
+        <v>123400</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Ceiling Finish</t>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Ceiling Finishes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ceiling finish to AD-02</t>
+          <t>Ceiling finish</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -621,158 +621,22 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>89.56</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>10000</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>87000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Floor Finish</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Floor tiling to A</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>80.86</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>1212900</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Wall Finish</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Plastering to walls in A</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>115.46</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>1385520</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Skirting</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Skirting to A</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>35.97</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>89925</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Ceiling Finish</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Ceiling finish to A</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>80.86</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>808600</v>
+        <v>895600</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A7:F7"/>
+  <mergeCells count="5">
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/boq_styled.xlsx
+++ b/boq_styled.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="BoQ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -64,7 +65,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -79,6 +80,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -448,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -565,79 +571,151 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Superstructure Works</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Skirtings</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Skirting</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D9" s="4" t="n">
         <v>49.36</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E9" s="5" t="n">
         <v>2500</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F9" s="5" t="n">
         <v>123400</v>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="3" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Finishes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Ceiling Finishes</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Ceiling finish</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D12" s="4" t="n">
         <v>89.56</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E12" s="5" t="n">
         <v>10000</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F12" s="5" t="n">
         <v>895600</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B8:F8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Work Section</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Total (₦)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>SUPERSTRUCTURE WORKS</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>123400</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>FINISHES</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>4202920</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>GRAND TOTAL</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>4326320</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/boq_styled.xlsx
+++ b/boq_styled.xlsx
@@ -670,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,32 +686,62 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>SUPERSTRUCTURE WORKS</t>
-        </is>
-      </c>
       <c r="B2" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Superstructure Works</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
         <v>123400</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>FINISHES</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Finishes</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
         <v>4202920</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B10" s="8" t="n">
         <v>4326320</v>
       </c>
     </row>

--- a/boq_styled.xlsx
+++ b/boq_styled.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -500,14 +500,14 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Finishes</t>
+          <t>Substructure Works</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Floor Finishes</t>
+          <t>Foundations</t>
         </is>
       </c>
     </row>
@@ -519,28 +519,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Floor tiling</t>
+          <t>Foundations approx 1.0m deep</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>89.56</v>
+        <v>0</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>15000</v>
+        <v>30000</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1343400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Wall Finishes</t>
+          <t>Ground Floor Slab</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Plastering to walls</t>
+          <t>Reinforced concrete slab 0.15m thick</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>163.66</v>
+        <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>12000</v>
+        <v>35000</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1963920</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -580,7 +580,7 @@
     <row r="8">
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Skirtings</t>
+          <t>Windows</t>
         </is>
       </c>
     </row>
@@ -592,73 +592,585 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Skirting</t>
+          <t>W4 (1 no.)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>49.36</v>
+        <v>444</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>2500</v>
+        <v>40000</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>123400</v>
+        <v>17760000</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Finishes</t>
-        </is>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>W6 (1 no.)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>370</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>14800000</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Ceiling Finishes</t>
-        </is>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>W2 (1 no.)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>370</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>14800000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>W3 (1 no.)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2960000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Doors</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D4 (1 no.)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>370</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>45000</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>16650000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>W1 (1 no.)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2960000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Doors</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D3 (1 no.)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>518</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>45000</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>23310000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D1 (1 no.)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>45000</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>3330000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>W5 (1 no.)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>2960000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Doors</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D2 (1 no.)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>45000</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>3330000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Skirtings</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Skirting</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>123400</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Finishes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Floor Finishes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Floor tiling</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>89.56</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>1343400</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Wall Finishes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Wall plastering/painting</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>181.58</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>2178960</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Ceiling Finishes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>Ceiling finish</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D32" s="4" t="n">
         <v>89.56</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E32" s="5" t="n">
         <v>10000</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F32" s="5" t="n">
         <v>895600</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ceiling at approx 3.3m</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>General Works</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Preliminaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Site establishment, preliminaries</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Provisional &amp; Prime Cost Sums</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Provisional sum (allowance)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Superstructure Works</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Concrete structural works</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="19">
     <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B39:F39"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -702,7 +1214,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>123400</v>
+        <v>102983400</v>
       </c>
     </row>
     <row r="5">
@@ -712,7 +1224,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>4202920</v>
+        <v>4417960</v>
       </c>
     </row>
     <row r="6">
@@ -742,7 +1254,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>4326320</v>
+        <v>107401360</v>
       </c>
     </row>
   </sheetData>

--- a/boq_styled.xlsx
+++ b/boq_styled.xlsx
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>30000</v>
+        <v>35000</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>0</v>
@@ -564,7 +564,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>35000</v>
+        <v>38000</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
@@ -604,10 +604,10 @@
         <v>444</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>40000</v>
+        <v>42000</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>17760000</v>
+        <v>18648000</v>
       </c>
     </row>
     <row r="10">
@@ -630,10 +630,10 @@
         <v>370</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>40000</v>
+        <v>42000</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>14800000</v>
+        <v>15540000</v>
       </c>
     </row>
     <row r="11">
@@ -656,10 +656,10 @@
         <v>370</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>40000</v>
+        <v>42000</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>14800000</v>
+        <v>15540000</v>
       </c>
     </row>
     <row r="12">
@@ -682,10 +682,10 @@
         <v>74</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>40000</v>
+        <v>42000</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>2960000</v>
+        <v>3108000</v>
       </c>
     </row>
     <row r="13">
@@ -715,10 +715,10 @@
         <v>370</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>16650000</v>
+        <v>18500000</v>
       </c>
     </row>
     <row r="15">
@@ -748,10 +748,10 @@
         <v>74</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>40000</v>
+        <v>42000</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>2960000</v>
+        <v>3108000</v>
       </c>
     </row>
     <row r="17">
@@ -781,10 +781,10 @@
         <v>518</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>23310000</v>
+        <v>25900000</v>
       </c>
     </row>
     <row r="19">
@@ -807,10 +807,10 @@
         <v>74</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>3330000</v>
+        <v>3700000</v>
       </c>
     </row>
     <row r="20">
@@ -840,10 +840,10 @@
         <v>74</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>40000</v>
+        <v>42000</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>2960000</v>
+        <v>3108000</v>
       </c>
     </row>
     <row r="22">
@@ -873,10 +873,10 @@
         <v>74</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>3330000</v>
+        <v>3700000</v>
       </c>
     </row>
     <row r="24">
@@ -906,10 +906,10 @@
         <v>49.36</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>123400</v>
+        <v>148080</v>
       </c>
     </row>
     <row r="26">
@@ -946,10 +946,10 @@
         <v>89.56</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>1343400</v>
+        <v>1432960</v>
       </c>
     </row>
     <row r="29">
@@ -979,10 +979,10 @@
         <v>181.58</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>2178960</v>
+        <v>2360540</v>
       </c>
     </row>
     <row r="31">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>102983400</v>
+        <v>111000080</v>
       </c>
     </row>
     <row r="5">
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>4417960</v>
+        <v>4689100</v>
       </c>
     </row>
     <row r="6">
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>107401360</v>
+        <v>115689180</v>
       </c>
     </row>
   </sheetData>
